--- a/outputs/20260809/idf_availability_summary_by_month.xlsx
+++ b/outputs/20260809/idf_availability_summary_by_month.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -389,97 +389,97 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BSH64-04</t>
+          <t>BSH52-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="C2">
-        <v>1373.483333333333</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>17879.73333333333</v>
+        <v>11044.46666666667</v>
       </c>
       <c r="E2">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F2">
-        <v>7.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BSH70-02</t>
+          <t>BSH61-06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="C3">
-        <v>186.6833333333333</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>17879.73333333333</v>
+        <v>11044.46666666667</v>
       </c>
       <c r="E3">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BSH52-11</t>
+          <t>BSH64-04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="C4">
-        <v>126.6833333333333</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>17879.73333333333</v>
+        <v>11044.46666666667</v>
       </c>
       <c r="E4">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F4">
-        <v>0.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BSH61-06</t>
+          <t>BSH70-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="C5">
-        <v>126.6833333333333</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>17879.73333333333</v>
+        <v>11044.46666666667</v>
       </c>
       <c r="E5">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F5">
-        <v>0.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -490,17 +490,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>22194.65</v>
+        <v>17900.91666666667</v>
       </c>
       <c r="E6">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -514,17 +514,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7">
-        <v>22194.65</v>
+        <v>17900.91666666667</v>
       </c>
       <c r="E7">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -538,17 +538,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>22194.65</v>
+        <v>17900.91666666667</v>
       </c>
       <c r="E8">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -562,17 +562,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>22194.65</v>
+        <v>17900.91666666667</v>
       </c>
       <c r="E9">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -586,17 +586,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>23910.63333333333</v>
+        <v>17334.15</v>
       </c>
       <c r="E10">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -610,17 +610,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>23910.63333333333</v>
+        <v>17334.15</v>
       </c>
       <c r="E11">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -634,17 +634,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>23910.63333333333</v>
+        <v>17334.15</v>
       </c>
       <c r="E12">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -658,17 +658,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>23910.63333333333</v>
+        <v>17334.15</v>
       </c>
       <c r="E13">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -677,121 +677,121 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BSH52-11</t>
+          <t>BSH61-06</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>140.6</v>
       </c>
       <c r="D14">
-        <v>26848.55</v>
+        <v>17917.16666666667</v>
       </c>
       <c r="E14">
         <v>31</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BSH61-06</t>
+          <t>BSH70-02</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>140.6</v>
       </c>
       <c r="D15">
-        <v>26848.55</v>
+        <v>17917.16666666667</v>
       </c>
       <c r="E15">
         <v>31</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BSH64-04</t>
+          <t>BSH52-11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D16">
-        <v>26848.55</v>
+        <v>17917.16666666667</v>
       </c>
       <c r="E16">
         <v>31</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BSH70-02</t>
+          <t>BSH64-04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D17">
-        <v>26848.55</v>
+        <v>17917.16666666667</v>
       </c>
       <c r="E17">
         <v>31</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BSH52-11</t>
+          <t>BSH64-04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="C18">
-        <v>3475.2</v>
+        <v>1373.483333333333</v>
       </c>
       <c r="D18">
-        <v>27055.2</v>
+        <v>17879.73333333333</v>
       </c>
       <c r="E18">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F18">
-        <v>12.8</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="19">
@@ -802,44 +802,44 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="C19">
-        <v>3433.95</v>
+        <v>186.6833333333333</v>
       </c>
       <c r="D19">
-        <v>27055.2</v>
+        <v>17879.73333333333</v>
       </c>
       <c r="E19">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F19">
-        <v>12.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BSH64-04</t>
+          <t>BSH52-11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="C20">
-        <v>3420.416666666667</v>
+        <v>126.6833333333333</v>
       </c>
       <c r="D20">
-        <v>27055.2</v>
+        <v>17879.73333333333</v>
       </c>
       <c r="E20">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F20">
-        <v>12.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="21">
@@ -850,19 +850,403 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>126.6833333333333</v>
+      </c>
+      <c r="D21">
+        <v>17879.73333333333</v>
+      </c>
+      <c r="E21">
+        <v>28</v>
+      </c>
+      <c r="F21">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>BSH52-11</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>22194.65</v>
+      </c>
+      <c r="E22">
+        <v>31</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>BSH61-06</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>22194.65</v>
+      </c>
+      <c r="E23">
+        <v>31</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>BSH64-04</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>22194.65</v>
+      </c>
+      <c r="E24">
+        <v>31</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>BSH70-02</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>22194.65</v>
+      </c>
+      <c r="E25">
+        <v>31</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>BSH52-11</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>23910.63333333333</v>
+      </c>
+      <c r="E26">
+        <v>30</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BSH61-06</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>23910.63333333333</v>
+      </c>
+      <c r="E27">
+        <v>30</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>BSH64-04</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>23910.63333333333</v>
+      </c>
+      <c r="E28">
+        <v>30</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>BSH70-02</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <v>23910.63333333333</v>
+      </c>
+      <c r="E29">
+        <v>30</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BSH52-11</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <v>26848.55</v>
+      </c>
+      <c r="E30">
+        <v>31</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BSH61-06</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>26848.55</v>
+      </c>
+      <c r="E31">
+        <v>31</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BSH64-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32">
+        <v>26848.55</v>
+      </c>
+      <c r="E32">
+        <v>31</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>BSH70-02</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
+      <c r="D33">
+        <v>26848.55</v>
+      </c>
+      <c r="E33">
+        <v>31</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>BSH52-11</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="C21">
+      <c r="C34">
+        <v>3475.2</v>
+      </c>
+      <c r="D34">
+        <v>27055.2</v>
+      </c>
+      <c r="E34">
+        <v>30</v>
+      </c>
+      <c r="F34">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>BSH70-02</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>3433.95</v>
+      </c>
+      <c r="D35">
+        <v>27055.2</v>
+      </c>
+      <c r="E35">
+        <v>30</v>
+      </c>
+      <c r="F35">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>BSH64-04</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>3420.416666666667</v>
+      </c>
+      <c r="D36">
+        <v>27055.2</v>
+      </c>
+      <c r="E36">
+        <v>30</v>
+      </c>
+      <c r="F36">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BSH61-06</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C37">
         <v>3416.766666666666</v>
       </c>
-      <c r="D21">
+      <c r="D37">
         <v>27055.2</v>
       </c>
-      <c r="E21">
+      <c r="E37">
         <v>30</v>
       </c>
-      <c r="F21">
+      <c r="F37">
         <v>12.6</v>
       </c>
     </row>
